--- a/samples/예시데이터_8월재고분석(본사).xlsx
+++ b/samples/예시데이터_8월재고분석(본사).xlsx
@@ -3,10 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="8월 원자재(본사)" sheetId="1" r:id="rId1"/>
-    <sheet name="7월 원자재(본사)" sheetId="2" r:id="rId2"/>
-    <sheet name="8월제품" sheetId="3" r:id="rId3"/>
-    <sheet name="7월제품" sheetId="4" r:id="rId4"/>
+    <sheet name="원자재" sheetId="1" r:id="rId1"/>
+    <sheet name="반제품" sheetId="2" r:id="rId2"/>
+    <sheet name="제품" sheetId="3" r:id="rId3"/>
+    <sheet name="8월 원자재(본사)" sheetId="4" r:id="rId4"/>
+    <sheet name="7월 원자재(본사)" sheetId="5" r:id="rId5"/>
+    <sheet name="8월반제품(본사)" sheetId="6" r:id="rId6"/>
+    <sheet name="7월반제품(본사)" sheetId="7" r:id="rId7"/>
+    <sheet name="8월제품" sheetId="8" r:id="rId8"/>
+    <sheet name="7월제품" sheetId="9" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
@@ -400,6 +405,592 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>본사기준</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>구분</v>
+      </c>
+      <c r="B2" t="str">
+        <v>대분류</v>
+      </c>
+      <c r="C2" t="str">
+        <v>재고현황(07월)</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v>재고현황(08월)</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>수량 증감 비교 (08월재고현황 - 07월재고현황)</v>
+      </c>
+      <c r="H2" t="str">
+        <v>금액 증감 비교 (08월재고현황 - 07월재고현황)</v>
+      </c>
+      <c r="I2" t="str">
+        <v>원인분석</v>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v>비고</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v xml:space="preserve"> 수량</v>
+      </c>
+      <c r="D3" t="str">
+        <v>금액</v>
+      </c>
+      <c r="E3" t="str">
+        <v xml:space="preserve"> 수량</v>
+      </c>
+      <c r="F3" t="str">
+        <v>금액</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>07월 재고현황</v>
+      </c>
+      <c r="J3" t="str">
+        <v>08월 재고현황</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>원자재</v>
+      </c>
+      <c r="B4" t="str">
+        <v>하우징류</v>
+      </c>
+      <c r="C4">
+        <v>20300</v>
+      </c>
+      <c r="D4">
+        <v>6280000</v>
+      </c>
+      <c r="E4">
+        <v>21700</v>
+      </c>
+      <c r="F4">
+        <v>5984000</v>
+      </c>
+      <c r="G4">
+        <v>1400</v>
+      </c>
+      <c r="H4">
+        <v>-296000</v>
+      </c>
+      <c r="I4" t="str">
+        <v>3종</v>
+      </c>
+      <c r="J4" t="str">
+        <v>3종</v>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v>씰류</v>
+      </c>
+      <c r="C5">
+        <v>50000</v>
+      </c>
+      <c r="D5">
+        <v>600000</v>
+      </c>
+      <c r="E5">
+        <v>42000</v>
+      </c>
+      <c r="F5">
+        <v>504000</v>
+      </c>
+      <c r="G5">
+        <v>-8000</v>
+      </c>
+      <c r="H5">
+        <v>-96000</v>
+      </c>
+      <c r="I5" t="str">
+        <v>1종</v>
+      </c>
+      <c r="J5" t="str">
+        <v>1종</v>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v/>
+      </c>
+      <c r="B6" t="str">
+        <v>터미널류</v>
+      </c>
+      <c r="C6">
+        <v>110000</v>
+      </c>
+      <c r="D6">
+        <v>4810000</v>
+      </c>
+      <c r="E6">
+        <v>102000</v>
+      </c>
+      <c r="F6">
+        <v>4460000</v>
+      </c>
+      <c r="G6">
+        <v>-8000</v>
+      </c>
+      <c r="H6">
+        <v>-350000</v>
+      </c>
+      <c r="I6" t="str">
+        <v>2종</v>
+      </c>
+      <c r="J6" t="str">
+        <v>2종</v>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v>와이어류</v>
+      </c>
+      <c r="C7">
+        <v>30000</v>
+      </c>
+      <c r="D7">
+        <v>2850000</v>
+      </c>
+      <c r="E7">
+        <v>31000</v>
+      </c>
+      <c r="F7">
+        <v>3410000</v>
+      </c>
+      <c r="G7">
+        <v>1000</v>
+      </c>
+      <c r="H7">
+        <v>560000</v>
+      </c>
+      <c r="I7" t="str">
+        <v>1종</v>
+      </c>
+      <c r="J7" t="str">
+        <v>1종</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v/>
+      </c>
+      <c r="B8" t="str">
+        <v>클립류</v>
+      </c>
+      <c r="C8">
+        <v>4000</v>
+      </c>
+      <c r="D8">
+        <v>120000</v>
+      </c>
+      <c r="E8">
+        <v>4000</v>
+      </c>
+      <c r="F8">
+        <v>120000</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" t="str">
+        <v>1종</v>
+      </c>
+      <c r="J8" t="str">
+        <v>1종</v>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v/>
+      </c>
+      <c r="B9" t="str">
+        <v>기타</v>
+      </c>
+      <c r="C9">
+        <v>1700</v>
+      </c>
+      <c r="D9">
+        <v>122000</v>
+      </c>
+      <c r="E9">
+        <v>2300</v>
+      </c>
+      <c r="F9">
+        <v>270000</v>
+      </c>
+      <c r="G9">
+        <v>600</v>
+      </c>
+      <c r="H9">
+        <v>148000</v>
+      </c>
+      <c r="I9" t="str">
+        <v>2종</v>
+      </c>
+      <c r="J9" t="str">
+        <v>2종</v>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v/>
+      </c>
+      <c r="B10" t="str">
+        <v>합계</v>
+      </c>
+      <c r="C10">
+        <v>216000</v>
+      </c>
+      <c r="D10">
+        <v>14783000</v>
+      </c>
+      <c r="E10">
+        <v>203000</v>
+      </c>
+      <c r="F10">
+        <v>14748000</v>
+      </c>
+      <c r="G10">
+        <v>-13000</v>
+      </c>
+      <c r="H10">
+        <v>-35000</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>본사기준</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>구분</v>
+      </c>
+      <c r="B2" t="str">
+        <v>07월 재고현황</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v>08월 재고현황</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>재고잔량분석</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v xml:space="preserve"> 수량</v>
+      </c>
+      <c r="C3" t="str">
+        <v>금액</v>
+      </c>
+      <c r="D3" t="str">
+        <v xml:space="preserve"> 수량</v>
+      </c>
+      <c r="E3" t="str">
+        <v>금액</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>예시고객사 1</v>
+      </c>
+      <c r="B4">
+        <v>120</v>
+      </c>
+      <c r="C4">
+        <v>1080000</v>
+      </c>
+      <c r="D4">
+        <v>150</v>
+      </c>
+      <c r="E4">
+        <v>1350000</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>예시고객사 2</v>
+      </c>
+      <c r="B5">
+        <v>40</v>
+      </c>
+      <c r="C5">
+        <v>600000</v>
+      </c>
+      <c r="D5">
+        <v>40</v>
+      </c>
+      <c r="E5">
+        <v>600000</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>총합계</v>
+      </c>
+      <c r="B6">
+        <v>160</v>
+      </c>
+      <c r="C6">
+        <v>1680000</v>
+      </c>
+      <c r="D6">
+        <v>190</v>
+      </c>
+      <c r="E6">
+        <v>1950000</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G7"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>본사기준</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>구분</v>
+      </c>
+      <c r="B2" t="str">
+        <v>07월 재고현황</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v>08월 재고현황</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>재고잔량분석</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v xml:space="preserve"> 수량</v>
+      </c>
+      <c r="C3" t="str">
+        <v>금액</v>
+      </c>
+      <c r="D3" t="str">
+        <v xml:space="preserve"> 수량</v>
+      </c>
+      <c r="E3" t="str">
+        <v>금액</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>예시고객사 1</v>
+      </c>
+      <c r="B4">
+        <v>660</v>
+      </c>
+      <c r="C4">
+        <v>12920000</v>
+      </c>
+      <c r="D4">
+        <v>700</v>
+      </c>
+      <c r="E4">
+        <v>13320000</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>예시고객사 2</v>
+      </c>
+      <c r="B5">
+        <v>590</v>
+      </c>
+      <c r="C5">
+        <v>9150000</v>
+      </c>
+      <c r="D5">
+        <v>830</v>
+      </c>
+      <c r="E5">
+        <v>12400000</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>예시고객사 3</v>
+      </c>
+      <c r="B6">
+        <v>120</v>
+      </c>
+      <c r="C6">
+        <v>4920000</v>
+      </c>
+      <c r="D6">
+        <v>300</v>
+      </c>
+      <c r="E6">
+        <v>4500000</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>총합계</v>
+      </c>
+      <c r="B7">
+        <v>1370</v>
+      </c>
+      <c r="C7">
+        <v>26990000</v>
+      </c>
+      <c r="D7">
+        <v>1830</v>
+      </c>
+      <c r="E7">
+        <v>30220000</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J12"/>
   <sheetData>
     <row r="1">
@@ -766,7 +1357,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J12"/>
   <sheetData>
@@ -1134,7 +1725,231 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>회사명 : 예시회사(가상) / 예시-반제품-본사창고 외 / 2026/08/31  / 재고현황</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>품목코드</v>
+      </c>
+      <c r="B2" t="str">
+        <v>품목명[규격]</v>
+      </c>
+      <c r="C2" t="str">
+        <v>대분류</v>
+      </c>
+      <c r="D2" t="str">
+        <v>재고수량</v>
+      </c>
+      <c r="E2" t="str">
+        <v>완제품단가</v>
+      </c>
+      <c r="F2" t="str">
+        <v>재고*완제품단가</v>
+      </c>
+      <c r="G2" t="str">
+        <v>반제품단가</v>
+      </c>
+      <c r="H2" t="str">
+        <v>합계금액</v>
+      </c>
+      <c r="I2" t="str">
+        <v>재고잔량</v>
+      </c>
+      <c r="J2" t="str">
+        <v>고객사</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SF-101</v>
+      </c>
+      <c r="B3" t="str">
+        <v>예시반제품 가 [SUB]</v>
+      </c>
+      <c r="C3" t="str">
+        <v>반제품</v>
+      </c>
+      <c r="D3">
+        <v>150</v>
+      </c>
+      <c r="E3">
+        <v>13500</v>
+      </c>
+      <c r="F3">
+        <v>2025000</v>
+      </c>
+      <c r="G3">
+        <v>9000</v>
+      </c>
+      <c r="H3">
+        <v>1350000</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3" t="str">
+        <v>예시고객사 1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SF-102</v>
+      </c>
+      <c r="B4" t="str">
+        <v>예시반제품 나 [SUB]</v>
+      </c>
+      <c r="C4" t="str">
+        <v>반제품</v>
+      </c>
+      <c r="D4">
+        <v>40</v>
+      </c>
+      <c r="E4">
+        <v>22500</v>
+      </c>
+      <c r="F4">
+        <v>900000</v>
+      </c>
+      <c r="G4">
+        <v>15000</v>
+      </c>
+      <c r="H4">
+        <v>600000</v>
+      </c>
+      <c r="I4" t="str">
+        <v>8 개월</v>
+      </c>
+      <c r="J4" t="str">
+        <v>예시고객사 2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>회사명 : 예시회사(가상) / 예시-반제품-본사창고 외 / 2026/07/31  / 재고현황</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>품목코드</v>
+      </c>
+      <c r="B2" t="str">
+        <v>품목명[규격]</v>
+      </c>
+      <c r="C2" t="str">
+        <v>대분류</v>
+      </c>
+      <c r="D2" t="str">
+        <v>재고수량</v>
+      </c>
+      <c r="E2" t="str">
+        <v>완제품단가</v>
+      </c>
+      <c r="F2" t="str">
+        <v>재고*완제품단가</v>
+      </c>
+      <c r="G2" t="str">
+        <v>반제품단가</v>
+      </c>
+      <c r="H2" t="str">
+        <v>합계금액</v>
+      </c>
+      <c r="I2" t="str">
+        <v>재고잔량</v>
+      </c>
+      <c r="J2" t="str">
+        <v>고객사</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SF-101</v>
+      </c>
+      <c r="B3" t="str">
+        <v>예시반제품 가 [SUB]</v>
+      </c>
+      <c r="C3" t="str">
+        <v>반제품</v>
+      </c>
+      <c r="D3">
+        <v>120</v>
+      </c>
+      <c r="E3">
+        <v>13500</v>
+      </c>
+      <c r="F3">
+        <v>1620000</v>
+      </c>
+      <c r="G3">
+        <v>9000</v>
+      </c>
+      <c r="H3">
+        <v>1080000</v>
+      </c>
+      <c r="I3" t="str">
+        <v>1 개월</v>
+      </c>
+      <c r="J3" t="str">
+        <v>예시고객사 1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SF-102</v>
+      </c>
+      <c r="B4" t="str">
+        <v>예시반제품 나 [SUB]</v>
+      </c>
+      <c r="C4" t="str">
+        <v>반제품</v>
+      </c>
+      <c r="D4">
+        <v>40</v>
+      </c>
+      <c r="E4">
+        <v>22500</v>
+      </c>
+      <c r="F4">
+        <v>900000</v>
+      </c>
+      <c r="G4">
+        <v>15000</v>
+      </c>
+      <c r="H4">
+        <v>600000</v>
+      </c>
+      <c r="I4" t="str">
+        <v>7 개월</v>
+      </c>
+      <c r="J4" t="str">
+        <v>예시고객사 2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H7"/>
   <sheetData>
@@ -1306,7 +2121,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H7"/>
   <sheetData>

--- a/samples/예시데이터_8월재고분석(본사).xlsx
+++ b/samples/예시데이터_8월재고분석(본사).xlsx
@@ -3,15 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="원자재" sheetId="1" r:id="rId1"/>
-    <sheet name="반제품" sheetId="2" r:id="rId2"/>
-    <sheet name="제품" sheetId="3" r:id="rId3"/>
-    <sheet name="8월 원자재(본사)" sheetId="4" r:id="rId4"/>
-    <sheet name="7월 원자재(본사)" sheetId="5" r:id="rId5"/>
-    <sheet name="8월반제품(본사)" sheetId="6" r:id="rId6"/>
-    <sheet name="7월반제품(본사)" sheetId="7" r:id="rId7"/>
-    <sheet name="8월제품" sheetId="8" r:id="rId8"/>
-    <sheet name="7월제품" sheetId="9" r:id="rId9"/>
+    <sheet name="총괄현황" sheetId="1" r:id="rId1"/>
+    <sheet name="원자재" sheetId="2" r:id="rId2"/>
+    <sheet name="반제품" sheetId="3" r:id="rId3"/>
+    <sheet name="제품" sheetId="4" r:id="rId4"/>
+    <sheet name="8월 원자재(본사)" sheetId="5" r:id="rId5"/>
+    <sheet name="7월 원자재(본사)" sheetId="6" r:id="rId6"/>
+    <sheet name="8월반제품(본사)" sheetId="7" r:id="rId7"/>
+    <sheet name="7월반제품(본사)" sheetId="8" r:id="rId8"/>
+    <sheet name="8월제품" sheetId="9" r:id="rId9"/>
+    <sheet name="7월제품" sheetId="10" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
@@ -405,6 +406,354 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F9"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>본사기준</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>구분</v>
+      </c>
+      <c r="B2" t="str">
+        <v>항목</v>
+      </c>
+      <c r="C2" t="str">
+        <v>26년 07월</v>
+      </c>
+      <c r="D2" t="str">
+        <v>26년 08월</v>
+      </c>
+      <c r="E2" t="str">
+        <v>증감</v>
+      </c>
+      <c r="F2" t="str">
+        <v>비고</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>자재</v>
+      </c>
+      <c r="B3" t="str">
+        <v>정상</v>
+      </c>
+      <c r="C3">
+        <v>14.8</v>
+      </c>
+      <c r="D3">
+        <v>14.7</v>
+      </c>
+      <c r="E3">
+        <v>-0.1</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v/>
+      </c>
+      <c r="B4" t="str">
+        <v>불용</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>반제품</v>
+      </c>
+      <c r="B5" t="str">
+        <v>정상</v>
+      </c>
+      <c r="C5">
+        <v>1.7</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>0.3</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v/>
+      </c>
+      <c r="B6" t="str">
+        <v>불용</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>제품</v>
+      </c>
+      <c r="B7" t="str">
+        <v>정상</v>
+      </c>
+      <c r="C7">
+        <v>27</v>
+      </c>
+      <c r="D7">
+        <v>30.2</v>
+      </c>
+      <c r="E7">
+        <v>3.2</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v/>
+      </c>
+      <c r="B8" t="str">
+        <v>불용</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>계</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H7"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>회사명 : 예시회사(가상) / 예시-완제품-본사창고 외 / 2026/07/31  / 재고현황</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>품목코드</v>
+      </c>
+      <c r="B2" t="str">
+        <v>품목명[규격]</v>
+      </c>
+      <c r="C2" t="str">
+        <v>대분류</v>
+      </c>
+      <c r="D2" t="str">
+        <v>재고수량</v>
+      </c>
+      <c r="E2" t="str">
+        <v>완제품단가</v>
+      </c>
+      <c r="F2" t="str">
+        <v>재고*완제품단가</v>
+      </c>
+      <c r="G2" t="str">
+        <v>고객사</v>
+      </c>
+      <c r="H2" t="str">
+        <v>재고잔량</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>FG-501</v>
+      </c>
+      <c r="B3" t="str">
+        <v>예시제품 가</v>
+      </c>
+      <c r="C3" t="str">
+        <v>완제품</v>
+      </c>
+      <c r="D3">
+        <v>400</v>
+      </c>
+      <c r="E3">
+        <v>18000</v>
+      </c>
+      <c r="F3">
+        <v>7200000</v>
+      </c>
+      <c r="G3" t="str">
+        <v>예시고객사 1</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>FG-502</v>
+      </c>
+      <c r="B4" t="str">
+        <v>예시제품 나</v>
+      </c>
+      <c r="C4" t="str">
+        <v>완제품</v>
+      </c>
+      <c r="D4">
+        <v>260</v>
+      </c>
+      <c r="E4">
+        <v>22000</v>
+      </c>
+      <c r="F4">
+        <v>5720000</v>
+      </c>
+      <c r="G4" t="str">
+        <v>예시고객사 1</v>
+      </c>
+      <c r="H4" t="str">
+        <v>1 개월</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>FG-503</v>
+      </c>
+      <c r="B5" t="str">
+        <v>예시제품 다</v>
+      </c>
+      <c r="C5" t="str">
+        <v>완제품</v>
+      </c>
+      <c r="D5">
+        <v>90</v>
+      </c>
+      <c r="E5">
+        <v>35000</v>
+      </c>
+      <c r="F5">
+        <v>3150000</v>
+      </c>
+      <c r="G5" t="str">
+        <v>예시고객사 2</v>
+      </c>
+      <c r="H5" t="str">
+        <v>12 개월</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>FG-504</v>
+      </c>
+      <c r="B6" t="str">
+        <v>예시제품 라</v>
+      </c>
+      <c r="C6" t="str">
+        <v>완제품</v>
+      </c>
+      <c r="D6">
+        <v>500</v>
+      </c>
+      <c r="E6">
+        <v>12000</v>
+      </c>
+      <c r="F6">
+        <v>6000000</v>
+      </c>
+      <c r="G6" t="str">
+        <v>예시고객사 2</v>
+      </c>
+      <c r="H6" t="str">
+        <v>1 개월</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>FG-506</v>
+      </c>
+      <c r="B7" t="str">
+        <v>예시제품 바</v>
+      </c>
+      <c r="C7" t="str">
+        <v>완제품</v>
+      </c>
+      <c r="D7">
+        <v>120</v>
+      </c>
+      <c r="E7">
+        <v>41000</v>
+      </c>
+      <c r="F7">
+        <v>4920000</v>
+      </c>
+      <c r="G7" t="str">
+        <v>예시고객사 3</v>
+      </c>
+      <c r="H7" t="str">
+        <v>3 개월</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K10"/>
   <sheetData>
     <row r="1">
@@ -731,7 +1080,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G6"/>
   <sheetData>
@@ -850,7 +1199,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G7"/>
   <sheetData>
@@ -985,374 +1334,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J12"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>회사명 : 예시회사(가상) / 예시-자재-본사창고 외 / 2026/08/31  / 재고현황</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>품목코드</v>
-      </c>
-      <c r="B2" t="str">
-        <v>품목명[규격]</v>
-      </c>
-      <c r="C2" t="str">
-        <v>대분류</v>
-      </c>
-      <c r="D2" t="str">
-        <v>재고보유월수</v>
-      </c>
-      <c r="E2" t="str">
-        <v>재고수량</v>
-      </c>
-      <c r="F2" t="str">
-        <v>가용수량</v>
-      </c>
-      <c r="G2" t="str">
-        <v>입고단가</v>
-      </c>
-      <c r="H2" t="str">
-        <v>금액(재고수량*입고단가)</v>
-      </c>
-      <c r="I2" t="str">
-        <v>재고잔량분석</v>
-      </c>
-      <c r="J2" t="str">
-        <v>비고</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>H-1001</v>
-      </c>
-      <c r="B3" t="str">
-        <v>예시 하우징 6P [HSG]</v>
-      </c>
-      <c r="C3" t="str">
-        <v>HSG</v>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3">
-        <v>15000</v>
-      </c>
-      <c r="F3">
-        <v>15000</v>
-      </c>
-      <c r="G3">
-        <v>120</v>
-      </c>
-      <c r="H3">
-        <v>1800000</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>H-1002</v>
-      </c>
-      <c r="B4" t="str">
-        <v>예시 하우징 12P [HSG]</v>
-      </c>
-      <c r="C4" t="str">
-        <v>HSG</v>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4">
-        <v>6400</v>
-      </c>
-      <c r="F4">
-        <v>6400</v>
-      </c>
-      <c r="G4">
-        <v>410</v>
-      </c>
-      <c r="H4">
-        <v>2624000</v>
-      </c>
-      <c r="I4" t="str">
-        <v>3 개월</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>H-1003</v>
-      </c>
-      <c r="B5" t="str">
-        <v>예시 하우징 2P [HSG]</v>
-      </c>
-      <c r="C5" t="str">
-        <v>HSG</v>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5">
-        <v>300</v>
-      </c>
-      <c r="F5">
-        <v>300</v>
-      </c>
-      <c r="G5">
-        <v>5200</v>
-      </c>
-      <c r="H5">
-        <v>1560000</v>
-      </c>
-      <c r="I5" t="str">
-        <v>12 개월초과</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>S-2001</v>
-      </c>
-      <c r="B6" t="str">
-        <v>예시 씰 A</v>
-      </c>
-      <c r="C6" t="str">
-        <v>SEAL</v>
-      </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6">
-        <v>42000</v>
-      </c>
-      <c r="F6">
-        <v>42000</v>
-      </c>
-      <c r="G6">
-        <v>12</v>
-      </c>
-      <c r="H6">
-        <v>504000</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>T-3001</v>
-      </c>
-      <c r="B7" t="str">
-        <v>예시 터미널 A [TML]</v>
-      </c>
-      <c r="C7" t="str">
-        <v>TML</v>
-      </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7">
-        <v>76000</v>
-      </c>
-      <c r="F7">
-        <v>76000</v>
-      </c>
-      <c r="G7">
-        <v>45</v>
-      </c>
-      <c r="H7">
-        <v>3420000</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>T-3002</v>
-      </c>
-      <c r="B8" t="str">
-        <v>예시 터미널 B [TML]</v>
-      </c>
-      <c r="C8" t="str">
-        <v>TML</v>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8">
-        <v>26000</v>
-      </c>
-      <c r="F8">
-        <v>26000</v>
-      </c>
-      <c r="G8">
-        <v>40</v>
-      </c>
-      <c r="H8">
-        <v>1040000</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>W-4001</v>
-      </c>
-      <c r="B9" t="str">
-        <v>예시 전선 0.5SQ</v>
-      </c>
-      <c r="C9" t="str">
-        <v>WIRE</v>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9">
-        <v>31000</v>
-      </c>
-      <c r="F9">
-        <v>31000</v>
-      </c>
-      <c r="G9">
-        <v>110</v>
-      </c>
-      <c r="H9">
-        <v>3410000</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>C-5001</v>
-      </c>
-      <c r="B10" t="str">
-        <v>예시 클립 A</v>
-      </c>
-      <c r="C10" t="str">
-        <v>CLIP</v>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10">
-        <v>4000</v>
-      </c>
-      <c r="F10">
-        <v>4000</v>
-      </c>
-      <c r="G10">
-        <v>30</v>
-      </c>
-      <c r="H10">
-        <v>120000</v>
-      </c>
-      <c r="I10" t="str">
-        <v>8 개월</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>G-6001</v>
-      </c>
-      <c r="B11" t="str">
-        <v>예시 그로멧 A</v>
-      </c>
-      <c r="C11" t="str">
-        <v>GROMMET</v>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11">
-        <v>1800</v>
-      </c>
-      <c r="F11">
-        <v>1800</v>
-      </c>
-      <c r="G11">
-        <v>150</v>
-      </c>
-      <c r="H11">
-        <v>270000</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>X-7002</v>
-      </c>
-      <c r="B12" t="str">
-        <v>예시 기타자재 A</v>
-      </c>
-      <c r="C12" t="str">
-        <v/>
-      </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-      <c r="E12">
-        <v>500</v>
-      </c>
-      <c r="F12">
-        <v>500</v>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>7 개월</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J12"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1363,7 +1344,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>회사명 : 예시회사(가상) / 예시-자재-본사창고 외 / 2026/07/31  / 재고현황</v>
+        <v>회사명 : 예시회사(가상) / 예시-자재-본사창고 외 / 2026/08/31  / 재고현황</v>
       </c>
     </row>
     <row r="2">
@@ -1412,19 +1393,19 @@
         <v/>
       </c>
       <c r="E3">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="F3">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="G3">
         <v>120</v>
       </c>
       <c r="H3">
-        <v>1440000</v>
-      </c>
-      <c r="I3" t="str">
-        <v>1 개월</v>
+        <v>1800000</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -1444,19 +1425,19 @@
         <v/>
       </c>
       <c r="E4">
-        <v>8000</v>
+        <v>6400</v>
       </c>
       <c r="F4">
-        <v>8000</v>
+        <v>6400</v>
       </c>
       <c r="G4">
         <v>410</v>
       </c>
       <c r="H4">
-        <v>3280000</v>
+        <v>2624000</v>
       </c>
       <c r="I4" t="str">
-        <v>2 개월</v>
+        <v>3 개월</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -1488,7 +1469,7 @@
         <v>1560000</v>
       </c>
       <c r="I5" t="str">
-        <v>12 개월</v>
+        <v>12 개월초과</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -1508,16 +1489,16 @@
         <v/>
       </c>
       <c r="E6">
-        <v>50000</v>
+        <v>42000</v>
       </c>
       <c r="F6">
-        <v>50000</v>
+        <v>42000</v>
       </c>
       <c r="G6">
         <v>12</v>
       </c>
       <c r="H6">
-        <v>600000</v>
+        <v>504000</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1540,16 +1521,16 @@
         <v/>
       </c>
       <c r="E7">
-        <v>90000</v>
+        <v>76000</v>
       </c>
       <c r="F7">
-        <v>90000</v>
+        <v>76000</v>
       </c>
       <c r="G7">
         <v>45</v>
       </c>
       <c r="H7">
-        <v>4050000</v>
+        <v>3420000</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1572,19 +1553,19 @@
         <v/>
       </c>
       <c r="E8">
-        <v>20000</v>
+        <v>26000</v>
       </c>
       <c r="F8">
-        <v>20000</v>
+        <v>26000</v>
       </c>
       <c r="G8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H8">
-        <v>760000</v>
-      </c>
-      <c r="I8" t="str">
-        <v>1 개월</v>
+        <v>1040000</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -1604,16 +1585,16 @@
         <v/>
       </c>
       <c r="E9">
-        <v>30000</v>
+        <v>31000</v>
       </c>
       <c r="F9">
-        <v>30000</v>
+        <v>31000</v>
       </c>
       <c r="G9">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="H9">
-        <v>2850000</v>
+        <v>3410000</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1648,7 +1629,7 @@
         <v>120000</v>
       </c>
       <c r="I10" t="str">
-        <v>7 개월</v>
+        <v>8 개월</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -1656,31 +1637,31 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>X-7001</v>
+        <v>G-6001</v>
       </c>
       <c r="B11" t="str">
-        <v>예시 테이프 A</v>
+        <v>예시 그로멧 A</v>
       </c>
       <c r="C11" t="str">
-        <v>TAPE</v>
+        <v>GROMMET</v>
       </c>
       <c r="D11" t="str">
         <v/>
       </c>
       <c r="E11">
-        <v>1200</v>
+        <v>1800</v>
       </c>
       <c r="F11">
-        <v>1200</v>
+        <v>1800</v>
       </c>
       <c r="G11">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H11">
-        <v>72000</v>
-      </c>
-      <c r="I11" t="str">
-        <v>4 개월</v>
+        <v>270000</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -1705,14 +1686,14 @@
       <c r="F12">
         <v>500</v>
       </c>
-      <c r="G12">
-        <v>100</v>
-      </c>
-      <c r="H12">
-        <v>50000</v>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>6 개월</v>
+        <v>7 개월</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -1727,11 +1708,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>회사명 : 예시회사(가상) / 예시-반제품-본사창고 외 / 2026/08/31  / 재고현황</v>
+        <v>회사명 : 예시회사(가상) / 예시-자재-본사창고 외 / 2026/07/31  / 재고현황</v>
       </c>
     </row>
     <row r="2">
@@ -1745,94 +1726,350 @@
         <v>대분류</v>
       </c>
       <c r="D2" t="str">
+        <v>재고보유월수</v>
+      </c>
+      <c r="E2" t="str">
         <v>재고수량</v>
       </c>
-      <c r="E2" t="str">
-        <v>완제품단가</v>
-      </c>
       <c r="F2" t="str">
-        <v>재고*완제품단가</v>
+        <v>가용수량</v>
       </c>
       <c r="G2" t="str">
-        <v>반제품단가</v>
+        <v>입고단가</v>
       </c>
       <c r="H2" t="str">
-        <v>합계금액</v>
+        <v>금액(재고수량*입고단가)</v>
       </c>
       <c r="I2" t="str">
-        <v>재고잔량</v>
+        <v>재고잔량분석</v>
       </c>
       <c r="J2" t="str">
-        <v>고객사</v>
+        <v>비고</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SF-101</v>
+        <v>H-1001</v>
       </c>
       <c r="B3" t="str">
-        <v>예시반제품 가 [SUB]</v>
+        <v>예시 하우징 6P [HSG]</v>
       </c>
       <c r="C3" t="str">
-        <v>반제품</v>
-      </c>
-      <c r="D3">
-        <v>150</v>
+        <v>HSG</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
       </c>
       <c r="E3">
-        <v>13500</v>
+        <v>12000</v>
       </c>
       <c r="F3">
-        <v>2025000</v>
+        <v>12000</v>
       </c>
       <c r="G3">
-        <v>9000</v>
+        <v>120</v>
       </c>
       <c r="H3">
-        <v>1350000</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
+        <v>1440000</v>
+      </c>
+      <c r="I3" t="str">
+        <v>1 개월</v>
       </c>
       <c r="J3" t="str">
-        <v>예시고객사 1</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SF-102</v>
+        <v>H-1002</v>
       </c>
       <c r="B4" t="str">
-        <v>예시반제품 나 [SUB]</v>
+        <v>예시 하우징 12P [HSG]</v>
       </c>
       <c r="C4" t="str">
-        <v>반제품</v>
-      </c>
-      <c r="D4">
-        <v>40</v>
+        <v>HSG</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
       </c>
       <c r="E4">
-        <v>22500</v>
+        <v>8000</v>
       </c>
       <c r="F4">
-        <v>900000</v>
+        <v>8000</v>
       </c>
       <c r="G4">
-        <v>15000</v>
+        <v>410</v>
       </c>
       <c r="H4">
+        <v>3280000</v>
+      </c>
+      <c r="I4" t="str">
+        <v>2 개월</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>H-1003</v>
+      </c>
+      <c r="B5" t="str">
+        <v>예시 하우징 2P [HSG]</v>
+      </c>
+      <c r="C5" t="str">
+        <v>HSG</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5">
+        <v>300</v>
+      </c>
+      <c r="F5">
+        <v>300</v>
+      </c>
+      <c r="G5">
+        <v>5200</v>
+      </c>
+      <c r="H5">
+        <v>1560000</v>
+      </c>
+      <c r="I5" t="str">
+        <v>12 개월</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>S-2001</v>
+      </c>
+      <c r="B6" t="str">
+        <v>예시 씰 A</v>
+      </c>
+      <c r="C6" t="str">
+        <v>SEAL</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6">
+        <v>50000</v>
+      </c>
+      <c r="F6">
+        <v>50000</v>
+      </c>
+      <c r="G6">
+        <v>12</v>
+      </c>
+      <c r="H6">
         <v>600000</v>
       </c>
-      <c r="I4" t="str">
-        <v>8 개월</v>
-      </c>
-      <c r="J4" t="str">
-        <v>예시고객사 2</v>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>T-3001</v>
+      </c>
+      <c r="B7" t="str">
+        <v>예시 터미널 A [TML]</v>
+      </c>
+      <c r="C7" t="str">
+        <v>TML</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7">
+        <v>90000</v>
+      </c>
+      <c r="F7">
+        <v>90000</v>
+      </c>
+      <c r="G7">
+        <v>45</v>
+      </c>
+      <c r="H7">
+        <v>4050000</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>T-3002</v>
+      </c>
+      <c r="B8" t="str">
+        <v>예시 터미널 B [TML]</v>
+      </c>
+      <c r="C8" t="str">
+        <v>TML</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8">
+        <v>20000</v>
+      </c>
+      <c r="F8">
+        <v>20000</v>
+      </c>
+      <c r="G8">
+        <v>38</v>
+      </c>
+      <c r="H8">
+        <v>760000</v>
+      </c>
+      <c r="I8" t="str">
+        <v>1 개월</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>W-4001</v>
+      </c>
+      <c r="B9" t="str">
+        <v>예시 전선 0.5SQ</v>
+      </c>
+      <c r="C9" t="str">
+        <v>WIRE</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9">
+        <v>30000</v>
+      </c>
+      <c r="F9">
+        <v>30000</v>
+      </c>
+      <c r="G9">
+        <v>95</v>
+      </c>
+      <c r="H9">
+        <v>2850000</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>C-5001</v>
+      </c>
+      <c r="B10" t="str">
+        <v>예시 클립 A</v>
+      </c>
+      <c r="C10" t="str">
+        <v>CLIP</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10">
+        <v>4000</v>
+      </c>
+      <c r="F10">
+        <v>4000</v>
+      </c>
+      <c r="G10">
+        <v>30</v>
+      </c>
+      <c r="H10">
+        <v>120000</v>
+      </c>
+      <c r="I10" t="str">
+        <v>7 개월</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>X-7001</v>
+      </c>
+      <c r="B11" t="str">
+        <v>예시 테이프 A</v>
+      </c>
+      <c r="C11" t="str">
+        <v>TAPE</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11">
+        <v>1200</v>
+      </c>
+      <c r="F11">
+        <v>1200</v>
+      </c>
+      <c r="G11">
+        <v>60</v>
+      </c>
+      <c r="H11">
+        <v>72000</v>
+      </c>
+      <c r="I11" t="str">
+        <v>4 개월</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>X-7002</v>
+      </c>
+      <c r="B12" t="str">
+        <v>예시 기타자재 A</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12">
+        <v>500</v>
+      </c>
+      <c r="F12">
+        <v>500</v>
+      </c>
+      <c r="G12">
+        <v>100</v>
+      </c>
+      <c r="H12">
+        <v>50000</v>
+      </c>
+      <c r="I12" t="str">
+        <v>6 개월</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J12"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1843,7 +2080,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>회사명 : 예시회사(가상) / 예시-반제품-본사창고 외 / 2026/07/31  / 재고현황</v>
+        <v>회사명 : 예시회사(가상) / 예시-반제품-본사창고 외 / 2026/08/31  / 재고현황</v>
       </c>
     </row>
     <row r="2">
@@ -1889,22 +2126,22 @@
         <v>반제품</v>
       </c>
       <c r="D3">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E3">
         <v>13500</v>
       </c>
       <c r="F3">
-        <v>1620000</v>
+        <v>2025000</v>
       </c>
       <c r="G3">
         <v>9000</v>
       </c>
       <c r="H3">
-        <v>1080000</v>
-      </c>
-      <c r="I3" t="str">
-        <v>1 개월</v>
+        <v>1350000</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
       </c>
       <c r="J3" t="str">
         <v>예시고객사 1</v>
@@ -1936,7 +2173,7 @@
         <v>600000</v>
       </c>
       <c r="I4" t="str">
-        <v>7 개월</v>
+        <v>8 개월</v>
       </c>
       <c r="J4" t="str">
         <v>예시고객사 2</v>
@@ -1951,11 +2188,11 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:J4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>회사명 : 예시회사(가상) / 예시-완제품-본사창고 외 / 2026/08/31  / 재고현황</v>
+        <v>회사명 : 예시회사(가상) / 예시-반제품-본사창고 외 / 2026/07/31  / 재고현황</v>
       </c>
     </row>
     <row r="2">
@@ -1978,145 +2215,85 @@
         <v>재고*완제품단가</v>
       </c>
       <c r="G2" t="str">
+        <v>반제품단가</v>
+      </c>
+      <c r="H2" t="str">
+        <v>합계금액</v>
+      </c>
+      <c r="I2" t="str">
+        <v>재고잔량</v>
+      </c>
+      <c r="J2" t="str">
         <v>고객사</v>
-      </c>
-      <c r="H2" t="str">
-        <v>재고잔량</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>FG-501</v>
+        <v>SF-101</v>
       </c>
       <c r="B3" t="str">
-        <v>예시제품 가</v>
+        <v>예시반제품 가 [SUB]</v>
       </c>
       <c r="C3" t="str">
-        <v>완제품</v>
+        <v>반제품</v>
       </c>
       <c r="D3">
-        <v>520</v>
+        <v>120</v>
       </c>
       <c r="E3">
-        <v>18000</v>
+        <v>13500</v>
       </c>
       <c r="F3">
-        <v>9360000</v>
-      </c>
-      <c r="G3" t="str">
+        <v>1620000</v>
+      </c>
+      <c r="G3">
+        <v>9000</v>
+      </c>
+      <c r="H3">
+        <v>1080000</v>
+      </c>
+      <c r="I3" t="str">
+        <v>1 개월</v>
+      </c>
+      <c r="J3" t="str">
         <v>예시고객사 1</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>FG-502</v>
+        <v>SF-102</v>
       </c>
       <c r="B4" t="str">
-        <v>예시제품 나</v>
+        <v>예시반제품 나 [SUB]</v>
       </c>
       <c r="C4" t="str">
-        <v>완제품</v>
+        <v>반제품</v>
       </c>
       <c r="D4">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="E4">
-        <v>22000</v>
+        <v>22500</v>
       </c>
       <c r="F4">
-        <v>3960000</v>
-      </c>
-      <c r="G4" t="str">
-        <v>예시고객사 1</v>
+        <v>900000</v>
+      </c>
+      <c r="G4">
+        <v>15000</v>
       </c>
       <c r="H4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>FG-503</v>
-      </c>
-      <c r="B5" t="str">
-        <v>예시제품 다</v>
-      </c>
-      <c r="C5" t="str">
-        <v>완제품</v>
-      </c>
-      <c r="D5">
-        <v>90</v>
-      </c>
-      <c r="E5">
-        <v>35000</v>
-      </c>
-      <c r="F5">
-        <v>3150000</v>
-      </c>
-      <c r="G5" t="str">
+        <v>600000</v>
+      </c>
+      <c r="I4" t="str">
+        <v>7 개월</v>
+      </c>
+      <c r="J4" t="str">
         <v>예시고객사 2</v>
-      </c>
-      <c r="H5" t="str">
-        <v>12 개월초과</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>FG-504</v>
-      </c>
-      <c r="B6" t="str">
-        <v>예시제품 라</v>
-      </c>
-      <c r="C6" t="str">
-        <v>완제품</v>
-      </c>
-      <c r="D6">
-        <v>740</v>
-      </c>
-      <c r="E6">
-        <v>12500</v>
-      </c>
-      <c r="F6">
-        <v>9250000</v>
-      </c>
-      <c r="G6" t="str">
-        <v>예시고객사 2</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>FG-505</v>
-      </c>
-      <c r="B7" t="str">
-        <v>예시제품 마</v>
-      </c>
-      <c r="C7" t="str">
-        <v>상품</v>
-      </c>
-      <c r="D7">
-        <v>300</v>
-      </c>
-      <c r="E7">
-        <v>15000</v>
-      </c>
-      <c r="F7">
-        <v>4500000</v>
-      </c>
-      <c r="G7" t="str">
-        <v>예시고객사 3</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2127,7 +2304,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>회사명 : 예시회사(가상) / 예시-완제품-본사창고 외 / 2026/07/31  / 재고현황</v>
+        <v>회사명 : 예시회사(가상) / 예시-완제품-본사창고 외 / 2026/08/31  / 재고현황</v>
       </c>
     </row>
     <row r="2">
@@ -2167,13 +2344,13 @@
         <v>완제품</v>
       </c>
       <c r="D3">
-        <v>400</v>
+        <v>520</v>
       </c>
       <c r="E3">
         <v>18000</v>
       </c>
       <c r="F3">
-        <v>7200000</v>
+        <v>9360000</v>
       </c>
       <c r="G3" t="str">
         <v>예시고객사 1</v>
@@ -2193,19 +2370,19 @@
         <v>완제품</v>
       </c>
       <c r="D4">
-        <v>260</v>
+        <v>180</v>
       </c>
       <c r="E4">
         <v>22000</v>
       </c>
       <c r="F4">
-        <v>5720000</v>
+        <v>3960000</v>
       </c>
       <c r="G4" t="str">
         <v>예시고객사 1</v>
       </c>
-      <c r="H4" t="str">
-        <v>1 개월</v>
+      <c r="H4">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2231,7 +2408,7 @@
         <v>예시고객사 2</v>
       </c>
       <c r="H5" t="str">
-        <v>12 개월</v>
+        <v>12 개월초과</v>
       </c>
     </row>
     <row r="6">
@@ -2245,45 +2422,45 @@
         <v>완제품</v>
       </c>
       <c r="D6">
-        <v>500</v>
+        <v>740</v>
       </c>
       <c r="E6">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="F6">
-        <v>6000000</v>
+        <v>9250000</v>
       </c>
       <c r="G6" t="str">
         <v>예시고객사 2</v>
       </c>
-      <c r="H6" t="str">
-        <v>1 개월</v>
+      <c r="H6">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>FG-506</v>
+        <v>FG-505</v>
       </c>
       <c r="B7" t="str">
-        <v>예시제품 바</v>
+        <v>예시제품 마</v>
       </c>
       <c r="C7" t="str">
-        <v>완제품</v>
+        <v>상품</v>
       </c>
       <c r="D7">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="E7">
-        <v>41000</v>
+        <v>15000</v>
       </c>
       <c r="F7">
-        <v>4920000</v>
+        <v>4500000</v>
       </c>
       <c r="G7" t="str">
         <v>예시고객사 3</v>
       </c>
-      <c r="H7" t="str">
-        <v>3 개월</v>
+      <c r="H7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
